--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-02_departments_部署_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-02_departments_部署_テーブル詳細設計書.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち departments を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/schema.sql（KF-DD-003 v2.0 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜022 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.1 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -775,7 +775,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>schema.sql の末尾 3 件。本番投入は seed ファイルを分離して行う（課題 C-3）。</t>
+          <t>V1__init_schema.sql の末尾 5 件（Flyway が適用）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>現状は schema.sql（set_updated_at 関数・トリガを含む）の手動実行＋ spring.jpa.hibernate.ddl-auto=validate。列追加・索引追加は ALTER 文を別ファイルにし、将来 Flyway（V1__baseline.sql ＋ V2__… ）へ移行する（KF-DD-003 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1 は編集せず、列追加・索引追加は V2__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -875,261 +875,261 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="77.5" customHeight="1">
+    <row r="12" ht="48.5" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>C-4</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PK 制約名が未指定で命名規約と不統一</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="77.5" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>C-5</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>業務ルールの CHECK 制約が少ない</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="63" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C-6</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="77.5" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>departments に UNIQUE が無く、管理機能も無い</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>部署名の重複を DB が許す。オンライン処理に部署の登録・変更 API が無い（ONL-014 は R のみ）。初期 5 部署は V1__init_schema.sql の INSERT のみ。部署名変更は過去の申請・集計にも現在名で表示される（ONL-007）。</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>部署追加・改名は SQL 直接実行になる。重複部署の混入を防げない。</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>uq_departments_1 (name) を追加。部署管理 ONL の追加を検討（無効化用 is_active 列も）。</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>題名</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>解消内容</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>根拠（DDL／規格）</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>残る事項</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="106.5" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>C-1</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>updated_at が更新時に自動更新されない</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="92" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>C-2</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>解消済み（v2.0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="135.5" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>C-3</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>先頭の DROP TABLE ... CASCADE（開発用）、DDL、トリガ／関数、初期データ（休暇種別 11 件・部署 3 件）が 1 ファイルに同居している。ヘッダは『PostgreSQL 18／KF-DD-003 v2.0』に修正済みで、旧『H2 / PostgreSQL 共通』の記述は解消。</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>本番 DB で誤実行すると全データを失う。</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>schema.sql を DDL 本体（DROP なし）／ dev-reset.sql（DROP）／ seed（初期データ）に分割。将来 Flyway（V1__baseline.sql）へ移行。</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48.5" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>C-4</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>PK 制約名が未指定で命名規約と不統一</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>FK は fk_、UNIQUE は uq_、CHECK は ck_ で名前付けされているが、PK だけ無名（PostgreSQL が &lt;表&gt;_pkey を自動付与）。</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>運用上の実害は小さい。制約名での障害解析・ALTER 時に規約と揃わない。</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>新規作成時は CONSTRAINT pk_&lt;表&gt; PRIMARY KEY (id) とする（既存は ALTER TABLE ... RENAME CONSTRAINT）。</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="77.5" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>C-5</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>業務ルールの CHECK 制約が少ない</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>コード値の CHECK は主要列にあるが、日付の前後関係・数値の範囲・種別別必須列などは DB で守られずアプリ（Bean Validation／Service）のみで保証している。手動 SQL・バッチ・将来の別入口からは不正データを入れられる。</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>データ不整合の混入余地。各表の個別課題を参照。</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>各表の「推奨 CHECK」を追加（既存データが違反していないことを 10章の確認 SQL で先に確認）。</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="63" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>C-6</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>アプリ（Hikari）以外の接続は TimeZone が Asia/Tokyo とは限らない</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>手動 SQL の INSERT／UPDATE で created_at と updated_at トリガの値が 9 時間ずれる。</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>ALTER DATABASE kintaiflow SET timezone TO 'Asia/Tokyo'; を併用する（確認 SQL: SHOW timezone;）。</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="77.5" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>D-1</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>departments に UNIQUE が無く、管理機能も無い</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>部署名の重複を DB が許す。オンライン処理に部署の登録・変更 API が無い（ONL-014 は R のみ）。初期 3 部署は schema.sql の INSERT のみ。部署名変更は過去の申請・集計にも現在名で表示される（ONL-007）。</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>部署追加・改名は SQL 直接実行になる。重複部署の混入を防げない。</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>uq_departments_1 (name) を追加。部署管理 ONL の追加を検討（無効化用 is_active 列も）。</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>9.2b 解消済み（v2.0）の課題（履歴。この版で対応済み）</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>題名</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>解消内容</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>根拠（DDL／規格）</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>残る事項</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="106.5" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>C-1</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>updated_at が更新時に自動更新されない</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>全 9 表に BEFORE UPDATE FOR EACH ROW のトリガ trg_&lt;表&gt;_updated_at を追加し、共通関数 set_updated_at() が NEW.updated_at を CURRENT_TIMESTAMP にする。アプリは updated_at を SET しない（ONL-010〜012・019 の updated_at = ? は削除）。『未決（@PreUpdate か DB トリガ）』は DB トリガで決定。</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>トリガは値が変わらない UPDATE でも、明示指定された updated_at があっても、トランザクション開始時刻で上書きする（仕様）。TimeZone の前提は課題 C-6。</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>解消済み（v2.0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="92" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>TIMESTAMP のタイムゾーン前提が DB 側で固定されていない（アプリ接続）</t>
+          <t>schema.sql の構成（開発用 DROP・DDL・初期データが 1 ファイルに同居）／手動実行</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+          <t>schema.sql を廃止し Flyway（backend/src/main/resources/db/migration/V1__init_schema.sql）へ移行。V1 は DROP を含まず、DDL・トリガ・初期データ（休暇種別 11 件・部署 5 件）を持つ。ユーザーは V1 に含めずアプリの初期化処理（DevDataInitializer / BootstrapAdminInitializer）が作る。開発用の全消去は backend/db/reset-dev.sql に分離。V1 は編集せず、変更は V2 以降を追加する。ddl-auto=validate を継続。</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>アプリ以外の接続は対象外（課題 C-6）。</t>
+          <t>旧 schema.sql 由来の開発 DB は baseline-on-migrate で V1 適用済みとみなされ、V1 の追加列（users の 4 列）が入らない。reset-dev.sql で作り直す必要がある。</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限8時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更・承認待ち申請の承認者付け替え。</t>
+          <t>無効化・ロール変更・パスワード設定は、発行済み JWT に即時反映されない（有効期限2時間まで旧権限のまま）。トークン失効・初回ログイン時のパスワード強制変更のサーバー側実施（画面側は ONL-023 で実装済み）・承認待ち申請の承認者付け替え。</t>
         </is>
       </c>
       <c r="D26" s="9" t="n"/>
@@ -1226,7 +1226,7 @@
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C24:F24"/>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>初期 3 件（運用で増加）</t>
+          <t>初期 5 件（運用で増加）</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>運用判断（初期は 人事部=1 名／開発部=0 名）</t>
+          <t>運用判断（本番は初期管理者 1 名のみのため、管理部以外は 0 名。開発用 100 名を入れた場合は全部署に所属あり）</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -1461,7 +1461,7 @@
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -1495,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1554,6 +1554,29 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="48.5" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql（Flyway）に移行し、初期部署を 3 件から 5 件（管理部／システム開発事業部／ソリューション事業部／SAP事業部／クラウド基盤サービス部）に変更。課題 C-3 を解消済みへ更新。</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1631,7 +1654,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>PostgreSQL 18 / UTF-8。DDL の正は backend/schema.sql。</t>
+          <t>PostgreSQL 18 / UTF-8。DDL の正は Flyway の V1__init_schema.sql（backend/src/main/resources/db/migration）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -1639,7 +1662,7 @@
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="10" t="n"/>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>想定件数</t>
@@ -1647,7 +1670,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>3 件（初期：人事部・営業部・開発部）。想定件数/年：〜20（企業の部署数であり年次増加ではない）</t>
+          <t>5 件（初期：管理部・システム開発事業部・ソリューション事業部・SAP事業部・クラウド基盤サービス部）。想定件数/年：〜20（企業の部署数であり年次増加ではない）</t>
         </is>
       </c>
       <c r="C6" s="9" t="n"/>
@@ -2123,10 +2146,10 @@
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="19.5" customHeight="1">
+    <row r="33" ht="63" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>backend/schema.sql</t>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -2209,7 +2232,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2.1 列定義（schema.sql から自動生成）</t>
+          <t>2.1 列定義（V1__init_schema.sql から自動生成）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -2397,7 +2420,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>初期データ（schema.sql の INSERT）または運用 SQL で設定。管理 API なし（課題 D-1）。</t>
+          <t>初期データ（V1__init_schema.sql の INSERT）または運用 SQL で設定。管理 API なし（課題 D-1）。</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -2523,7 +2546,7 @@
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
+          <t>キー：PK=主キー／FK=外部キー／UQ=単一列 UNIQUE／UQ*=複合 UNIQUE の構成列。型・桁・NULL・既定値は V1__init_schema.sql の定義。『使用ONL』は ONL 規格の mapping で『○』（その処理で使用）とされたもの。「DB の DEFAULT」はアプリが値を指定せず DB が設定する（Entity は insertable=false, updatable=false）。</t>
         </is>
       </c>
       <c r="B8" s="9" t="n"/>
@@ -2570,7 +2593,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>3.1 制約一覧（schema.sql の定義名のまま）</t>
+          <t>3.1 制約一覧（V1__init_schema.sql の定義名のまま）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -2853,7 +2876,7 @@
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>【適正】 ONL-007/009/014/018/020 の id 検索・結合で使用。3〜20 件のため問題なし。</t>
+          <t>【適正】 ONL-007/009/014/018/020 の id 検索・結合で使用。5〜20 件のため問題なし。</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
@@ -2863,7 +2886,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（schema.sql は変更しない。提案のみ。DDL は schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1__init_schema.sql＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B18" s="9" t="n"/>
@@ -4106,7 +4129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K23"/>
+  <dimension ref="A2:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4147,8 +4170,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>schema.sql が初期 3 部署を投入する。下記の INSERT は追加登録の例（運用 SQL）。
-例の INSERT は schema.sql 実行直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>V1__init_schema.sql が初期 5 部署を投入する。下記の INSERT は追加登録の例（運用 SQL）。
+例の INSERT は V1 適用直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
@@ -4215,7 +4238,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>人事部</t>
+          <t>管理部</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -4244,7 +4267,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>営業部</t>
+          <t>システム開発事業部</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -4273,7 +4296,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>開発部</t>
+          <t>ソリューション事業部</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -4294,7 +4317,7 @@
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>4</t>
@@ -4302,7 +4325,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>経理部（上記 INSERT の例）</t>
+          <t>SAP事業部</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -4323,15 +4346,56 @@
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n"/>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>8.3 INSERT 例（実際に実行できる SQL）</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>クラウド基盤サービス部</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>経理部（上記 INSERT の例）</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
@@ -4340,38 +4404,13 @@
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="10" t="n"/>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO departments(name) VALUES ('経理部');</t>
-        </is>
-      </c>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>8.3 INSERT 例（実際に実行できる SQL）</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
@@ -4382,13 +4421,38 @@
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>8.4 異常系の例（制約で拒否される INSERT。実行確認済み）</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n"/>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="19.5" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO departments(name) VALUES ('経理部');</t>
+        </is>
+      </c>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
@@ -4399,78 +4463,37 @@
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n"/>
     </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>ケース</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>SQL</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>結果（SQLSTATE）</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>name が NULL（NOT NULL 違反）</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO departments(name) VALUES (NULL);</t>
-        </is>
-      </c>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>8.4 異常系の例（制約で拒否される INSERT。実行確認済み）</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>23502 NOT NULL 違反</t>
-        </is>
-      </c>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n"/>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>name が 100 文字超（VARCHAR(100)）</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>INSERT INTO departments(name) VALUES (REPEAT('あ',101));</t>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>ケース</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>SQL</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -4478,106 +4501,166 @@
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>22001 文字列が長すぎる</t>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>結果（SQLSTATE）</t>
         </is>
       </c>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="10" t="n"/>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>8.5 updated_at 自動更新トリガの動作確認（UPDATE で updated_at が created_at より後になる）</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>name が NULL（NOT NULL 違反）</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO departments(name) VALUES (NULL);</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>23502 NOT NULL 違反</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>name が 100 文字超（VARCHAR(100)）</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO departments(name) VALUES (REPEAT('あ',101));</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>22001 文字列が長すぎる</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10" t="n"/>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>SQL（値は変更しない UPDATE。トリガにより updated_at のみ更新される）</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>WITH u AS (UPDATE departments SET name = name WHERE id = (SELECT MIN(id) FROM departments) RETURNING created_at, updated_at) SELECT updated_at &gt; created_at AS trigger_worked FROM u;</t>
-        </is>
-      </c>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>8.5 updated_at 自動更新トリガの動作確認（UPDATE で updated_at が created_at より後になる）</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>trigger_worked = true（8章のデータを投入済みの DB で、INSERT と別トランザクションの場合）</t>
-        </is>
-      </c>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="10" t="n"/>
     </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>SQL（値は変更しない UPDATE。トリガにより updated_at のみ更新される）</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>WITH u AS (UPDATE departments SET name = name WHERE id = (SELECT MIN(id) FROM departments) RETURNING created_at, updated_at) SELECT updated_at &gt; created_at AS trigger_worked FROM u;</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>trigger_worked = true（8章のデータを投入済みの DB で、INSERT と別トランザクションの場合）</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="I22:K22"/>
+  <mergeCells count="25">
     <mergeCell ref="D10:K10"/>
-    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I24:K24"/>
     <mergeCell ref="D6:K6"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="B16:K16"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="B3:K3"/>
     <mergeCell ref="I19:K19"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="C19:H19"/>
     <mergeCell ref="D7:K7"/>
-    <mergeCell ref="A21:K21"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="D12:K12"/>
     <mergeCell ref="D9:K9"/>
-    <mergeCell ref="B14:K14"/>
     <mergeCell ref="D8:K8"/>
-    <mergeCell ref="B13:K13"/>
+    <mergeCell ref="C20:H20"/>
+    <mergeCell ref="I25:K25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-02_departments_部署_テーブル詳細設計書.xlsx
+++ b/docs/03_詳細設計/03_テーブル設計/KF-DD-TBL-02_departments_部署_テーブル詳細設計書.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>本書の位置づけ：KF-DD-003 は全 9 テーブルの総覧（ER 図・CRUD マトリクス・規約）。本書はそのうち departments を、列・制約・索引・アクセスパターン・排他・運用まで実装/運用できる粒度で詳細化したもの。
-列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.1 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
+列・型・NULL・既定値・制約・索引・トリガは backend/src/main/resources/db/migration/V1__init_schema.sql（Flyway。KF-DD-003 v2.2 版。PostgreSQL 18）を解析して自動生成している（手書きで写していない）。アクセスパターンは ONL-001〜023 の規格（tables / mapping / sql）と BAT-001〜003 から自動抽出した。
 章番号は全テーブル共通。「4.状態遷移・コード値」は状態・コード値を持つ表（users / leave_types / requests / approval_steps / notifications）のみ作成している。</t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="10" t="n"/>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="48.5" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
           <t>初期データ</t>
@@ -775,7 +775,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>V1__init_schema.sql の末尾 5 件（Flyway が適用）。</t>
+          <t>V1__init_schema.sql の末尾 5 件（Flyway が適用）。id は 1=管理部、2=システム開発事業部、3=ソリューション事業部、4=SAP事業部、5=クラウド基盤サービス部（INSERT 順の採番）。DevDataInitializer は部署 ID 1〜5 を、BootstrapAdminInitializer は ID 1（管理部）を直接指定して users を作るため、V1 の INSERT 順・件数を変えず、部署行を削除・採番し直さないこと（FK 違反で起動に失敗する）。</t>
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。</t>
+          <t>毎日 03:30 に pg_dump（プレーン SQL、--clean --if-exists、REPEATABLE READ の単一スナップショット）で DB 全体を backup/kintai_yyyyMMdd.sql へ出力し 7 世代を保持（KF-DD-BAT-003）。復元後は IDENTITY の採番値（シーケンス）が最大 id を超えていることを確認する。なお BAT-001〜003 は設計のみで、現行の backend には実装が無い（@Scheduled・pg_dump 呼び出しなし）。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1 は編集せず、列追加・索引追加は V2__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
+          <t>Flyway（V1__init_schema.sql。set_updated_at 関数・トリガ・初期データを含む）＋ spring.jpa.hibernate.ddl-auto=validate。V1・V2（祝日の初期データ）は適用後に編集せず、列追加・索引追加は次の版 V3__… のように新しいファイルで行う（KF-DD-003・KF-DD-006 参照）。本書 3.4 の提案はこの方式で適用する。</t>
         </is>
       </c>
       <c r="C8" s="9" t="n"/>
@@ -939,7 +939,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="63" customHeight="1">
+    <row r="14" ht="77.5" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t>C-6</t>
@@ -952,7 +952,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>JST 固定は Hikari の connection-init-sql に依存する。psql での手動 SQL、マイグレーション実行、BAT-003 の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
+          <t>JST 固定は Hikari の connection-init-sql に依存する（Flyway はアプリの DataSource＝Hikari で実行するため JST）。psql での手動 SQL、BAT-003（設計）の pg_dump／復元、BI 接続は DB 既定の TimeZone（既定は UTC 等）で動く。</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="92" customHeight="1">
+    <row r="20" ht="135.5" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
           <t>C-2</t>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。hibernate.jdbc.time_zone=Asia/Tokyo で Timestamp 変換も JST。</t>
+          <t>spring.datasource.hikari.connection-init-sql = SET TIME ZONE 'Asia/Tokyo' で全接続を JST にし、DEFAULT CURRENT_TIMESTAMP と updated_at トリガも JST の壁時計時刻になる。業務時刻は Clock（ClockConfig / AppTime。Asia/Tokyo 固定）から取得した LocalDateTime をそのまま保存する。hibernate.jdbc.time_zone は設定していない（application.properties に無い）。Docker では ENV TZ=Asia/Tokyo。</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1458,10 +1458,10 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
+          <t>全 SQL を PostgreSQL 16 上で V1__init_schema.sql（v2.0・トリガ含む）＋ V2__seed_holidays.sql ＋ 8章のデータに対して実行し、構文と期待結果（8章データでの結果）を確認済み。件数確認系は参照のみで更新しない。</t>
         </is>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -1495,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1577,6 +1577,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="63" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>初期部署 5 件の ID（1〜5）に DevDataInitializer（部署 ID を直接指定）と BootstrapAdminInitializer（管理部＝ID 1）が依存することを運用に追記。V2（祝日の初期データ）追加に伴い、データ例の前提を V1・V2 適用直後に更新。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1591,7 +1614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F33"/>
+  <dimension ref="A2:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1774,15 +1797,15 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Entity クラス</t>
+          <t>初期データ</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>com.example.kintaiflow.entity.Department</t>
+          <t>V1__init_schema.sql の INSERT で 5 部署（管理部／システム開発事業部／ソリューション事業部／SAP事業部／クラウド基盤サービス部）。仮の部署名で、実際の組織に合わせて SQL で変更する（管理画面は無い。課題 D-1）。</t>
         </is>
       </c>
       <c r="C13" s="9" t="n"/>
@@ -1793,12 +1816,12 @@
     <row r="14" ht="19.5" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Entity クラス</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>repository.DepartmentRepository（findById / findAllById。ONL-007 で新規、ONL-014 が拡張）</t>
+          <t>com.example.kintaiflow.entity.Department</t>
         </is>
       </c>
       <c r="C14" s="9" t="n"/>
@@ -1806,84 +1829,76 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>repository.DepartmentRepository（findById / findAllById。ONL-007 で新規、ONL-014 が拡張）</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>1.2 主な利用処理（オンライン処理・バッチ）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="19.5" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>処理ID</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>処理名</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>API / 種別</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>CRUD</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>備考（規格 tables の注記ほか）</t>
         </is>
       </c>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>ONL-007</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>申請詳細取得</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>API-007 GET /api/requests/{id}</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr"/>
       <c r="F18" s="10" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>ONL-009</t>
+          <t>ONL-007</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>承認待ち一覧</t>
+          <t>申請詳細取得</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>API-009 GET /api/approvals/pending</t>
+          <t>API-007 GET /api/requests/{id}</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -1894,20 +1909,20 @@
       <c r="E19" s="7" t="inlineStr"/>
       <c r="F19" s="10" t="n"/>
     </row>
-    <row r="20" ht="48.5" customHeight="1">
+    <row r="20" ht="34" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>ONL-014</t>
+          <t>ONL-009</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ユーザー管理</t>
+          <t>承認待ち一覧</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>API-014 GET / POST / PUT /api/admin/users[/{id}[/password]]</t>
+          <t>API-009 GET /api/approvals/pending</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1918,20 +1933,20 @@
       <c r="E20" s="7" t="inlineStr"/>
       <c r="F20" s="10" t="n"/>
     </row>
-    <row r="21" ht="34" customHeight="1">
+    <row r="21" ht="48.5" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>ONL-018</t>
+          <t>ONL-014</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>月次集計取得</t>
+          <t>ユーザー管理</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>API-018 GET /api/admin/reports/monthly</t>
+          <t>API-014 GET / POST / PUT /api/admin/users[/{id}[/password]]</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -1945,17 +1960,17 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>ONL-020</t>
+          <t>ONL-018</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>上長の部下一覧</t>
+          <t>月次集計取得</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>API-020 GET /api/manager/subordinates/summary</t>
+          <t>API-018 GET /api/admin/reports/monthly</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -1969,77 +1984,81 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>ONL-020</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>上長の部下一覧</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>API-020 GET /api/manager/subordinates/summary</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>BAT-003</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>データバックアップ（pg_dump）</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>バッチ</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>pg_dump による全表読取（アプリ SQL なし）</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>1.3 関連設計書</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>文書番号</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>文書名</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>関連内容</t>
-        </is>
-      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
     <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>KF-DD-003</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>テーブル設計書（総覧）</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>文書番号</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>文書名</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>関連内容</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -2049,17 +2068,17 @@
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-003</t>
+          <t>KF-DD-003</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>テーブル定義書（基本）</t>
+          <t>テーブル設計書（総覧）</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>論理名・基本項目</t>
+          <t>ER 図・CRUD マトリクス・命名規約・型方針・マイグレーション方針</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -2069,17 +2088,17 @@
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>KF-BD-005</t>
+          <t>KF-BD-003</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>コード定義書</t>
+          <t>テーブル定義書（基本）</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>コード値と状態遷移の基本設計</t>
+          <t>論理名・基本項目</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -2089,17 +2108,17 @@
     <row r="30" ht="19.5" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-001</t>
+          <t>KF-BD-005</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>オンライン設計書</t>
+          <t>コード定義書</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>ONL-001〜022 の概要</t>
+          <t>コード値と状態遷移の基本設計</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2109,17 +2128,17 @@
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-ONL-xxx</t>
+          <t>KF-DD-001</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>オンライン詳細設計書</t>
+          <t>オンライン設計書</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>アクセスパターンの根拠（SQL・排他）</t>
+          <t>ONL-001〜022 の概要</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -2129,70 +2148,91 @@
     <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>KF-DD-004 / BAT</t>
+          <t>KF-DD-ONL-xxx</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>バッチ設計書</t>
+          <t>オンライン詳細設計書</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>BAT-001〜003 の使用</t>
+          <t>アクセスパターンの根拠（SQL・排他）</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="63" customHeight="1">
+    <row r="33" ht="19.5" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+          <t>KF-DD-004 / BAT</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>DDL 本体</t>
+          <t>バッチ設計書</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>本書の自動生成元</t>
+          <t>BAT-001〜003 の使用</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="10" t="n"/>
     </row>
+    <row r="34" ht="63" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>backend/src/main/resources/db/migration/V1__init_schema.sql</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>DDL 本体</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>本書の自動生成元</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="E23:F23"/>
     <mergeCell ref="C32:F32"/>
-    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C34:F34"/>
     <mergeCell ref="C30:F30"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="C27:F27"/>
@@ -2886,7 +2926,7 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1__init_schema.sql＋8章データに対して実行確認済み）</t>
+          <t>3.4 推奨する変更（V1__init_schema.sql は変更しない。提案のみ。DDL は V1・V2＋8章データに対して実行確認済み）</t>
         </is>
       </c>
       <c r="B18" s="9" t="n"/>
@@ -4170,8 +4210,8 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>V1__init_schema.sql が初期 5 部署を投入する。下記の INSERT は追加登録の例（運用 SQL）。
-例の INSERT は V1 適用直後の DB に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
+          <t>V1__init_schema.sql が初期 5 部署（id=1〜5）を投入する。下記の INSERT は追加登録の例（運用 SQL）。
+例の INSERT は V1・V2 適用直後の DB（開発用シードを入れていない状態）に、表の依存順（departments → leave_types → users → leave_balances → attendance_records → requests → approval_steps → holidays → notifications）で実行できる。外部キーは SELECT で解決しているため id の採番値に依存しない。PostgreSQL 16 で実行確認済み。</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
